--- a/docs/d/216/inyear.xlsx
+++ b/docs/d/216/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 81 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 78 clubs short</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4398,8 +4398,8 @@
       <c r="Y38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z38" s="9" t="n">
-        <v>0</v>
+      <c r="Z38" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA38" s="10" t="n">
         <v>1</v>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -5756,8 +5756,8 @@
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -10874,7 +10874,7 @@
         <v>2</v>
       </c>
       <c r="R105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S105" s="10" t="n">
         <v>2</v>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12837,8 +12837,8 @@
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="9" t="n">
-        <v>0</v>
+      <c r="Z125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -14876,7 +14876,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -14975,7 +14975,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15404,7 +15404,7 @@
         <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>

--- a/docs/d/216/inyear.xlsx
+++ b/docs/d/216/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/216/inyear.xlsx
+++ b/docs/d/216/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 78 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 73 clubs short</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
         <v>0</v>
       </c>
       <c r="S4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" s="9" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4107,8 +4107,8 @@
       <c r="Y35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" s="9" t="n">
-        <v>0</v>
+      <c r="Z35" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="AA35" s="10" t="n">
         <v>1</v>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -6074,7 +6074,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
@@ -6144,8 +6144,8 @@
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="10" t="n">
         <v>1</v>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8278,8 +8278,8 @@
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8666,8 +8666,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10024,8 +10024,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -14876,7 +14876,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -15008,7 +15008,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -15107,7 +15107,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -15140,7 +15140,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -15239,7 +15239,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>

--- a/docs/d/216/inyear.xlsx
+++ b/docs/d/216/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 73 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 44 clubs short</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1100,8 +1100,8 @@
       <c r="Y4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" s="9" t="n">
-        <v>0</v>
+      <c r="Z4" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA4" s="10" t="n">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1294,8 +1294,8 @@
       <c r="Y6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="9" t="n">
-        <v>0</v>
+      <c r="Z6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA6" s="10" t="n">
         <v>1</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1488,8 +1488,8 @@
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1585,8 +1585,8 @@
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="9" t="n">
-        <v>0</v>
+      <c r="Z9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1955,8 +1955,8 @@
       <c r="S13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T13" s="9" t="n">
-        <v>0</v>
+      <c r="T13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U13" s="9" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2167,8 +2167,8 @@
       <c r="Y15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" s="9" t="n">
-        <v>0</v>
+      <c r="Z15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA15" s="10" t="n">
         <v>1</v>
@@ -2652,8 +2652,8 @@
       <c r="Y20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="9" t="n">
-        <v>0</v>
+      <c r="Z20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA20" s="9" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -2943,8 +2943,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3313,8 +3313,8 @@
       <c r="S27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T27" s="9" t="n">
-        <v>0</v>
+      <c r="T27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U27" s="9" t="n">
         <v>0</v>
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3428,8 +3428,8 @@
       <c r="Y28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z28" s="9" t="n">
-        <v>0</v>
+      <c r="Z28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA28" s="10" t="n">
         <v>1</v>
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3719,8 +3719,8 @@
       <c r="Y31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z31" s="9" t="n">
-        <v>0</v>
+      <c r="Z31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>1</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -3913,8 +3913,8 @@
       <c r="Y33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="9" t="n">
-        <v>0</v>
+      <c r="Z33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="10" t="n">
         <v>1</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -4786,8 +4786,8 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="10" t="n">
         <v>1</v>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5556,14 +5556,14 @@
       <c r="W50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X50" s="9" t="n">
-        <v>2</v>
+      <c r="X50" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" s="9" t="n">
-        <v>0</v>
+      <c r="Z50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA50" s="10" t="n">
         <v>1</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -5853,8 +5853,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="n">
-        <v>0</v>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -5950,8 +5950,8 @@
       <c r="Y54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z54" s="9" t="n">
-        <v>0</v>
+      <c r="Z54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA54" s="10" t="n">
         <v>1</v>
@@ -6221,7 +6221,7 @@
         <v>0</v>
       </c>
       <c r="S57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" s="9" t="n">
         <v>0</v>
@@ -6333,7 +6333,7 @@
         <v>0</v>
       </c>
       <c r="X58" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y58" s="9" t="n">
         <v>0</v>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -6920,8 +6920,8 @@
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="9" t="n">
-        <v>0</v>
+      <c r="Z64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA64" s="10" t="n">
         <v>1</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7096,8 +7096,8 @@
       <c r="S66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T66" s="9" t="n">
-        <v>0</v>
+      <c r="T66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U66" s="9" t="n">
         <v>0</v>
@@ -7114,8 +7114,8 @@
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7405,8 +7405,8 @@
       <c r="Y69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" s="9" t="n">
-        <v>0</v>
+      <c r="Z69" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA69" s="10" t="n">
         <v>1</v>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8181,8 +8181,8 @@
       <c r="Y77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z77" s="9" t="n">
-        <v>0</v>
+      <c r="Z77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA77" s="10" t="n">
         <v>1</v>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8472,8 +8472,8 @@
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="9" t="n">
-        <v>0</v>
+      <c r="Z80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA80" s="10" t="n">
         <v>1</v>
@@ -8737,7 +8737,7 @@
         <v>2</v>
       </c>
       <c r="Q83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R83" s="9" t="n">
         <v>0</v>
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q84" s="9" t="n">
         <v>0</v>
@@ -9146,7 +9146,7 @@
         <v>0</v>
       </c>
       <c r="X87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y87" s="9" t="n">
         <v>0</v>
@@ -9275,7 +9275,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9345,8 +9345,8 @@
       <c r="Y89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" s="9" t="n">
-        <v>0</v>
+      <c r="Z89" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA89" s="10" t="n">
         <v>1</v>
@@ -9372,7 +9372,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9442,8 +9442,8 @@
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="9" t="n">
-        <v>0</v>
+      <c r="Z90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA90" s="10" t="n">
         <v>1</v>
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -10703,8 +10703,8 @@
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="9" t="n">
-        <v>0</v>
+      <c r="Z103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -10795,13 +10795,13 @@
         <v>0</v>
       </c>
       <c r="X104" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="9" t="n">
-        <v>0</v>
+      <c r="Z104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
@@ -10989,7 +10989,7 @@
         <v>0</v>
       </c>
       <c r="X106" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11673,8 +11673,8 @@
       <c r="Y113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" s="9" t="n">
-        <v>0</v>
+      <c r="Z113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA113" s="10" t="n">
         <v>1</v>
@@ -11700,7 +11700,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -11758,11 +11758,11 @@
       <c r="U114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V114" s="9" t="n">
-        <v>3</v>
+      <c r="V114" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X114" s="10" t="n">
         <v>6</v>
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12061,8 +12061,8 @@
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="9" t="n">
-        <v>0</v>
+      <c r="Z117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12255,8 +12255,8 @@
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="9" t="n">
-        <v>0</v>
+      <c r="Z119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA119" s="10" t="n">
         <v>1</v>
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12546,8 +12546,8 @@
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12638,13 +12638,13 @@
         <v>0</v>
       </c>
       <c r="X123" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z123" s="9" t="n">
-        <v>0</v>
+      <c r="Z123" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA123" s="10" t="n">
         <v>1</v>
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12934,8 +12934,8 @@
       <c r="Y126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z126" s="9" t="n">
-        <v>0</v>
+      <c r="Z126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA126" s="10" t="n">
         <v>1</v>
@@ -13414,7 +13414,7 @@
         <v>0</v>
       </c>
       <c r="X131" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
@@ -13511,7 +13511,7 @@
         <v>0</v>
       </c>
       <c r="X132" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y132" s="9" t="n">
         <v>0</v>
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14083,8 +14083,8 @@
       <c r="T138" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U138" s="9" t="n">
-        <v>0</v>
+      <c r="U138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V138" s="9" t="n">
         <v>0</v>
@@ -14222,7 +14222,7 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14274,8 +14274,8 @@
       <c r="S140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T140" s="9" t="n">
-        <v>0</v>
+      <c r="T140" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U140" s="9" t="n">
         <v>0</v>
@@ -14678,7 +14678,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -14711,7 +14711,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -14744,7 +14744,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -14777,7 +14777,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -14810,7 +14810,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -14843,7 +14843,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -14909,7 +14909,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -14942,7 +14942,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -14975,7 +14975,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15041,7 +15041,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -15074,7 +15074,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -15107,7 +15107,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -15140,7 +15140,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -15173,7 +15173,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15206,7 +15206,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15272,7 +15272,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -15305,7 +15305,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -15338,7 +15338,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15371,7 +15371,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15404,7 +15404,7 @@
         <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>0.71</v>
+        <v>0.86</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>

--- a/docs/d/216/inyear.xlsx
+++ b/docs/d/216/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 44 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 44 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1370,8 +1370,8 @@
       <c r="R7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S7" s="9" t="n">
-        <v>1</v>
+      <c r="S7" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T7" s="9" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1764,8 +1764,8 @@
       <c r="T11" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U11" s="9" t="n">
-        <v>0</v>
+      <c r="U11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V11" s="9" t="n">
         <v>1</v>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1917,17 +1917,17 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M13" s="8" t="n">
@@ -1953,7 +1953,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" s="10" t="n">
         <v>1</v>
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="P14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" s="9" t="n">
         <v>0</v>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2790,13 +2790,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -2819,8 +2819,8 @@
       <c r="P22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="9" t="n">
-        <v>1</v>
+      <c r="Q22" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R22" s="9" t="n">
         <v>0</v>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3275,17 +3275,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M27" s="8" t="n">
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3469,17 +3469,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="8" t="n">
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>0</v>
@@ -3514,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4051,17 +4051,17 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M35" s="8" t="n">
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>5</v>
+        <v>-10</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>1</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" s="9" t="n">
         <v>0</v>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
+        <v>-12</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5312,17 +5312,17 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-23</v>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M48" s="8" t="n">
@@ -5409,17 +5409,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M49" s="8" t="n">
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -5797,17 +5797,17 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M53" s="8" t="n">
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6088,17 +6088,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="8" t="n">
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6476,13 +6476,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6670,17 +6670,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-22</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="8" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -6961,17 +6961,17 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M65" s="8" t="n">
@@ -6991,7 +6991,7 @@
         <v>0</v>
       </c>
       <c r="Q65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R65" s="9" t="n">
         <v>0</v>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>0</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>0</v>
       </c>
       <c r="Q72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" s="9" t="n">
         <v>0</v>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -7931,17 +7931,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M75" s="8" t="n">
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8072,8 +8072,8 @@
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="9" t="n">
-        <v>2</v>
+      <c r="V76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>0</v>
       </c>
       <c r="V77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8319,17 +8319,17 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M79" s="8" t="n">
@@ -8364,7 +8364,7 @@
         <v>0</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" s="9" t="n">
         <v>0</v>
@@ -8561,7 +8561,7 @@
         <v>4</v>
       </c>
       <c r="W81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X81" s="10" t="n">
         <v>4</v>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>13</v>
+        <v>-5</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="P83" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q83" s="9" t="n">
         <v>1</v>
@@ -8755,7 +8755,7 @@
         <v>4</v>
       </c>
       <c r="W83" s="10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="X83" s="10" t="n">
         <v>5</v>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>3</v>
+        <v>-13</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -8945,8 +8945,8 @@
       <c r="U85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V85" s="9" t="n">
-        <v>3</v>
+      <c r="V85" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>3</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -9580,17 +9580,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -9625,7 +9625,7 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -9818,8 +9818,8 @@
       <c r="U94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V94" s="9" t="n">
-        <v>1</v>
+      <c r="V94" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>0</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10162,17 +10162,17 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M98" s="8" t="n">
@@ -10189,7 +10189,7 @@
         </is>
       </c>
       <c r="P98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q98" s="9" t="n">
         <v>0</v>
@@ -10259,17 +10259,17 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M99" s="8" t="n">
@@ -10295,7 +10295,7 @@
         <v>0</v>
       </c>
       <c r="S99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T99" s="9" t="n">
         <v>0</v>
@@ -10356,17 +10356,17 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M100" s="8" t="n">
@@ -10453,17 +10453,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M101" s="8" t="n">
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>1</v>
+        <v>-11</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11423,17 +11423,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -11467,8 +11467,8 @@
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="9" t="n">
-        <v>2</v>
+      <c r="V111" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -11714,17 +11714,17 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L114" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L114" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M114" s="8" t="n">
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -11811,17 +11811,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M115" s="8" t="n">
@@ -11840,8 +11840,8 @@
       <c r="P115" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q115" s="9" t="n">
-        <v>1</v>
+      <c r="Q115" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R115" s="9" t="n">
         <v>0</v>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -12781,13 +12781,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>0</v>
       </c>
       <c r="V125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>0</v>
       </c>
       <c r="V126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>4</v>
       </c>
       <c r="W130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X130" s="10" t="n">
         <v>5</v>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14042,17 +14042,17 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L138" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M138" s="8" t="n">
@@ -14087,7 +14087,7 @@
         <v>1</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
@@ -14139,13 +14139,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14236,17 +14236,17 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L140" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L140" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M140" s="8" t="n">
@@ -14281,7 +14281,7 @@
         <v>0</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -14711,7 +14711,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -14759,7 +14759,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -14777,7 +14777,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -14825,7 +14825,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -14891,7 +14891,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -14957,7 +14957,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -14990,7 +14990,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -15023,7 +15023,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -15056,7 +15056,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -15107,7 +15107,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -15122,7 +15122,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -15155,7 +15155,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -15173,7 +15173,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15206,7 +15206,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15221,7 +15221,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -15305,7 +15305,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -15320,7 +15320,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -15338,7 +15338,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15353,7 +15353,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -15485,7 +15485,7 @@
         <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/216/inyear.xlsx
+++ b/docs/d/216/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/216/inyear.xlsx
+++ b/docs/d/216/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/216/inyear.xlsx
+++ b/docs/d/216/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/216/inyear.xlsx
+++ b/docs/d/216/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/216/inyear.xlsx
+++ b/docs/d/216/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 44 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 44 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-12</v>
+        <v>1</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5312,17 +5312,17 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-23</v>
-      </c>
-      <c r="L48" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M48" s="8" t="n">
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6132,11 +6132,11 @@
       <c r="U56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V56" s="9" t="n">
-        <v>2</v>
+      <c r="V56" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X56" s="10" t="n">
         <v>5</v>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -6318,7 +6318,7 @@
         <v>0</v>
       </c>
       <c r="S58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" s="9" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -6999,8 +6999,8 @@
       <c r="S65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T65" s="9" t="n">
-        <v>0</v>
+      <c r="T65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U65" s="9" t="n">
         <v>0</v>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7931,17 +7931,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L75" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-3</v>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M75" s="8" t="n">
@@ -7976,7 +7976,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8066,8 +8066,8 @@
       <c r="S76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T76" s="9" t="n">
-        <v>0</v>
+      <c r="T76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U76" s="9" t="n">
         <v>0</v>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9139,8 +9139,8 @@
       <c r="U87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V87" s="9" t="n">
-        <v>3</v>
+      <c r="V87" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9509,8 +9509,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P91" s="9" t="n">
-        <v>3</v>
+      <c r="P91" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q91" s="9" t="n">
         <v>1</v>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -9812,11 +9812,11 @@
       <c r="S94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U94" s="9" t="n">
-        <v>0</v>
+      <c r="T94" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V94" s="10" t="n">
         <v>4</v>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-11</v>
+        <v>-6</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q110" s="9" t="n">
         <v>0</v>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -12631,8 +12631,8 @@
       <c r="U123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V123" s="9" t="n">
-        <v>0</v>
+      <c r="V123" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>4</v>
       </c>
       <c r="W130" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X130" s="10" t="n">
         <v>5</v>
@@ -14072,7 +14072,7 @@
         <v>0</v>
       </c>
       <c r="Q138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R138" s="9" t="n">
         <v>0</v>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -15008,7 +15008,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -15041,7 +15041,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -15107,7 +15107,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -15122,7 +15122,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -15173,7 +15173,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15206,7 +15206,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15371,7 +15371,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>

--- a/docs/d/216/inyear.xlsx
+++ b/docs/d/216/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 44 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 44 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="P12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="9" t="n">
         <v>0</v>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2152,8 +2152,8 @@
       <c r="T15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U15" s="9" t="n">
-        <v>0</v>
+      <c r="U15" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="V15" s="9" t="n">
         <v>1</v>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" s="10" t="n">
         <v>1</v>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4671,8 +4671,8 @@
       <c r="S41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T41" s="9" t="n">
-        <v>0</v>
+      <c r="T41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U41" s="9" t="n">
         <v>0</v>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="P66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q66" s="9" t="n">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q70" s="9" t="n">
         <v>1</v>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q72" s="9" t="n">
         <v>1</v>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8516,10 +8516,10 @@
         <v>31</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -8939,8 +8939,8 @@
       <c r="S85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T85" s="9" t="n">
-        <v>0</v>
+      <c r="T85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U85" s="9" t="n">
         <v>0</v>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="P90" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q90" s="9" t="n">
         <v>0</v>
@@ -10286,7 +10286,7 @@
         </is>
       </c>
       <c r="P99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q99" s="9" t="n">
         <v>1</v>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-15</v>
+        <v>-12</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11038,10 +11038,10 @@
         <v>14</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>1</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X111" s="10" t="n">
         <v>6</v>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>4</v>
       </c>
       <c r="W124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X124" s="10" t="n">
         <v>4</v>
@@ -12784,10 +12784,10 @@
         <v>13</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -14042,17 +14042,17 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L138" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M138" s="8" t="n">
@@ -14744,7 +14744,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -14909,7 +14909,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -15173,7 +15173,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15485,7 +15485,7 @@
         <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
